--- a/Jira/Plan de Prueba para Jira_y_Reportes de Bug/Modulo_Gestión de Transferencia/Reporte de  Bugs_Test Cases_Gestión de Transferencia -v 3.0.xlsx
+++ b/Jira/Plan de Prueba para Jira_y_Reportes de Bug/Modulo_Gestión de Transferencia/Reporte de  Bugs_Test Cases_Gestión de Transferencia -v 3.0.xlsx
@@ -5,9 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Portafolio\Plan de Prueba para Jira_y_Reportes de Bug\Modulo_Gestión de Transferencia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Portafolio\Jira\Plan de Prueba para Jira_y_Reportes de Bug\Modulo_Gestión de Transferencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="8R/xGd7OSnBedEHc/9/av3f84bQl2vYLrJJg1MsMDf0BnLmBxF/MGCpJjEPADgoEkraIvDxFjhiywsRzwjElNw==" workbookSaltValue="Esd38IZg0I3bdb12UgMFfQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715" activeTab="1"/>
   </bookViews>
@@ -1192,6 +1193,7 @@
       <c r="G14" s="38"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="fb6sCCXQhXlZuyg/8B1ERRNiqHnTi3kWBfF31/6oxcCXU+0AtqIOD1hWAL8iJuZ4KV0am78ccelTRsTrssKrOQ==" saltValue="f5HVxd5A6ZZWUX0NHU+GBg==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -1396,6 +1398,7 @@
     <row r="40" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="m7yM5FEFFUOYCGqTYpEzNHLWgEh49sirmxXFwQaWEaoBC+PzqzDhqrjb7eLd8XOZQiTC4yHBJp6ddkHt6YsPUA==" saltValue="bW3f9TsA87boE4p6uzAvOA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B20:C20"/>
